--- a/EXCEL/class notes/day5 data validation/DataValidation_V1.xlsx
+++ b/EXCEL/class notes/day5 data validation/DataValidation_V1.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day5 data validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A45C7A-7448-4FA5-9AEF-8139226A31AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB95C3CF-344D-45D2-A5F9-B8346918DE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{23AD2214-540B-487F-A675-0D9172F53C1C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{23AD2214-540B-487F-A675-0D9172F53C1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
     <sheet name="Home work" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Admin">'Home work'!$H$15:$H$18</definedName>
@@ -35,6 +34,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -619,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -659,8 +667,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -988,29 +994,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A5869E-DABA-471D-8A23-71D73BEAA2AF}">
   <dimension ref="B2:N22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="18"/>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="31" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="20"/>
@@ -1018,9 +1024,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="11"/>
-      <c r="C6" s="31"/>
       <c r="D6" s="12"/>
       <c r="F6" s="29" t="s">
         <v>20</v>
@@ -1030,11 +1035,10 @@
         <v>Name</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="31"/>
       <c r="D7" s="13" t="s">
         <v>98</v>
       </c>
@@ -1042,9 +1046,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="11"/>
-      <c r="C8" s="31"/>
       <c r="D8" s="12"/>
       <c r="K8" t="str">
         <f>C5</f>
@@ -1055,11 +1058,11 @@
         <v>Application form</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="7">
         <v>33</v>
       </c>
       <c r="D9" s="22">
@@ -1072,19 +1075,17 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
-      <c r="C10" s="31"/>
       <c r="D10" s="12"/>
       <c r="N10" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="31"/>
       <c r="D11" s="13" t="s">
         <v>104</v>
       </c>
@@ -1094,19 +1095,17 @@
         <v>$C$5</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="11"/>
-      <c r="C12" s="31"/>
       <c r="D12" s="12"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="31"/>
       <c r="D13" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>35</v>
@@ -1119,9 +1118,8 @@
       </c>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="11"/>
-      <c r="C14" s="31"/>
       <c r="D14" s="12"/>
       <c r="L14" s="8"/>
       <c r="N14" t="str">
@@ -1129,13 +1127,12 @@
         <v>Application form</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="31"/>
       <c r="D15" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -1152,9 +1149,8 @@
       </c>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
-      <c r="C16" s="31"/>
       <c r="D16" s="12"/>
       <c r="F16" t="s">
         <v>25</v>
@@ -1167,30 +1163,28 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="31"/>
       <c r="D17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="11"/>
-      <c r="C18" s="31"/>
       <c r="D18" s="12"/>
       <c r="F18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="15"/>
       <c r="C19" s="16"/>
       <c r="D19" s="17"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
         <v>105</v>
       </c>
@@ -1234,14 +1228,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B259DE28-C74D-4A60-A53E-6548A504FB47}">
   <dimension ref="B1:P22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" t="s">
         <v>101</v>
       </c>
@@ -1250,7 +1244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="21"/>
       <c r="D2" s="10"/>
@@ -1258,7 +1252,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="11"/>
       <c r="C3" s="7" t="s">
         <v>18</v>
@@ -1268,7 +1262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="11"/>
       <c r="D4" s="12"/>
       <c r="G4" s="8">
@@ -1286,7 +1280,7 @@
         <v>$D$6</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="D5" s="12"/>
       <c r="G5" s="8">
@@ -1296,7 +1290,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>90</v>
       </c>
@@ -1309,7 +1303,7 @@
         <v>$B$6</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -1321,7 +1315,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>32</v>
       </c>
@@ -1337,7 +1331,7 @@
         <v>Kamal</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -1350,7 +1344,7 @@
         <v>Emp Name</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
@@ -1371,7 +1365,7 @@
         <v>Kamal</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
@@ -1386,18 +1380,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F13" s="26" t="s">
         <v>29</v>
@@ -1412,18 +1406,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>57</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>59</v>
@@ -1441,7 +1435,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="D16" s="12"/>
       <c r="F16" s="4" t="s">
@@ -1454,7 +1448,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="15"/>
       <c r="C17" s="16"/>
       <c r="D17" s="17"/>
@@ -1468,7 +1462,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F18" s="4" t="s">
         <v>68</v>
       </c>
@@ -1479,17 +1473,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D19" s="29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D22" s="6" t="s">
         <v>96</v>
       </c>
@@ -1522,24 +1516,394 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A7B965-46D1-47AB-A309-90FA26C2D362}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>39</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>85</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>92</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>1014</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>1015</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2513AEB5-24A4-4CEA-B06C-76F0F576B2D2}">
+  <dimension ref="B3:H19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="18"/>
+      <c r="C4" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="F5" s="29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="D8" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="11"/>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="11"/>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="11"/>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="F15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="11"/>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please check input" promptTitle="Age limit" prompt="Enter age btween only 18 to 60" sqref="D8" xr:uid="{FB3267C9-DD80-45F1-AE7A-3E06BDE0F027}">
+      <formula1>18</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{6D7F3CC0-5B2A-43A2-8F16-8835F78D0277}">
+      <formula1>18</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D10" xr:uid="{F49D3E67-7354-49B7-8806-CB9965BED8D5}">
+      <formula1>"Male, Female"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12" xr:uid="{4BE1624F-2151-40DB-8D8E-7F25C32194D1}">
+      <formula1>$F$12:$H$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14" xr:uid="{59B12A43-DC3F-4438-8F21-06E4C8F314A0}">
+      <formula1>IF($D$12="BA",$F$14:$F$15,IF($D$12="B.Sc",$G$14:$G$15,$H$14:$H$15))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569B9C1C-7C6E-45D0-9B6B-A0FBB7727F1D}">
   <dimension ref="B2:J20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="9"/>
       <c r="C3" s="21"/>
       <c r="D3" s="10"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="11"/>
       <c r="C4" s="7" t="s">
         <v>18</v>
@@ -1552,7 +1916,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="D5" s="12"/>
       <c r="I5" t="s">
@@ -1562,7 +1926,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="11"/>
       <c r="D6" s="12"/>
       <c r="I6" t="s">
@@ -1572,7 +1936,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>1</v>
       </c>
@@ -1586,7 +1950,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="11"/>
       <c r="D8" s="12"/>
       <c r="I8" t="s">
@@ -1596,7 +1960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>32</v>
       </c>
@@ -1604,11 +1968,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
       <c r="D10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="11"/>
       <c r="D11" s="12" t="s">
         <v>51</v>
@@ -1617,7 +1981,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>33</v>
       </c>
@@ -1628,16 +1992,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="11"/>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>35</v>
@@ -1649,11 +2013,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="11"/>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
         <v>34</v>
       </c>
@@ -1670,7 +2034,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="11"/>
       <c r="D17" s="12"/>
       <c r="F17" t="s">
@@ -1683,12 +2047,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="15"/>
       <c r="C18" s="16"/>
       <c r="D18" s="17"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D20" s="24" t="s">
         <v>55</v>
       </c>
@@ -1718,198 +2082,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2513AEB5-24A4-4CEA-B06C-76F0F576B2D2}">
-  <dimension ref="B3:H19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="18"/>
-      <c r="C4" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="20"/>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="11"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="12"/>
-      <c r="F5" s="29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B6" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="11"/>
-      <c r="C7" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="32">
-        <v>23.5</v>
-      </c>
-      <c r="D8" s="22">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="11"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="12"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B11" s="11"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B13" s="11"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="11"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="12"/>
-      <c r="F15" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B17" s="11"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="G19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please check input" promptTitle="Age limit" prompt="Enter age btween only 18 to 60" sqref="D8" xr:uid="{FB3267C9-DD80-45F1-AE7A-3E06BDE0F027}">
-      <formula1>18</formula1>
-      <formula2>60</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{6D7F3CC0-5B2A-43A2-8F16-8835F78D0277}">
-      <formula1>18</formula1>
-      <formula2>60</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D10" xr:uid="{F49D3E67-7354-49B7-8806-CB9965BED8D5}">
-      <formula1>"Male, Female"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12" xr:uid="{4BE1624F-2151-40DB-8D8E-7F25C32194D1}">
-      <formula1>$F$12:$H$12</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14" xr:uid="{59B12A43-DC3F-4438-8F21-06E4C8F314A0}">
-      <formula1>IF($D$12="BA",$F$14:$F$15,IF($D$12="B.Sc",$G$14:$G$15,$H$14:$H$15))</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42293EFA-4B53-494F-82BD-BBA9234F045C}">
   <dimension ref="A1:M1000"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="J1" s="28" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F4" t="s">
         <v>0</v>
       </c>
@@ -1920,7 +2103,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" s="27">
         <v>8</v>
       </c>
@@ -1934,7 +2117,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" s="27">
         <v>7</v>
       </c>
@@ -1955,7 +2138,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" s="27">
         <v>9</v>
       </c>
@@ -1969,7 +2152,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" s="27">
         <v>4</v>
       </c>
@@ -1986,7 +2169,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F9">
         <v>1005</v>
       </c>
@@ -1997,7 +2180,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="C10">
         <f>SUM(MySales)</f>
@@ -2013,7 +2196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>72</v>
       </c>
@@ -2027,7 +2210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F12">
         <v>1008</v>
       </c>
@@ -2038,7 +2221,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F13">
         <v>1009</v>
       </c>
@@ -2049,7 +2232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F14">
         <v>1010</v>
       </c>
@@ -2060,7 +2243,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1000" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="1000" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J1000" s="8">
         <v>123</v>
       </c>
@@ -2074,213 +2257,4 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A7B965-46D1-47AB-A309-90FA26C2D362}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>39</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
-        <v>85</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
-        <v>92</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>1014</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B871C2-D8DD-47E0-A39B-2EFE151CAC4E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>